--- a/survey_templates/038_child_session_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/038_child_session_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -839,8 +839,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -868,12 +868,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': 'very_satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied',_'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied', 'value': 'satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied',_'value':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied', 'value': 'dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'high_-_fully_engaged',_'value':_'high'}</t>
+          <t>high_-_fully_engaged</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'High - Fully engaged', 'value': 'high'}</t>
+          <t>High - Fully engaged</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'moderate_-_mostly_focused',_'value':_'moderate'}</t>
+          <t>moderate_-_mostly_focused</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate - Mostly focused', 'value': 'moderate'}</t>
+          <t>Moderate - Mostly focused</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'low_-_struggles_with_focus',_'value':_'low'}</t>
+          <t>low_-_struggles_with_focus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Low - Struggles with focus', 'value': 'low'}</t>
+          <t>Low - Struggles with focus</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_please_call_me',_'value':_true}</t>
+          <t>yes_-_please_call_me</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Please call me', 'value': True}</t>
+          <t>Yes - Please call me</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_needed_at_this_time',_'value':_false}</t>
+          <t>no_-_not_needed_at_this_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not needed at this time', 'value': False}</t>
+          <t>No - Not needed at this time</t>
         </is>
       </c>
     </row>
